--- a/outputs/191-40.xlsx
+++ b/outputs/191-40.xlsx
@@ -259,10 +259,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.#"/>
+    <numFmt numFmtId="165" formatCode="##0.0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00_);&quot;($&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +291,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -365,35 +372,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -589,40 +596,40 @@
   <dimension ref="A1:L250"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="5.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="2.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="5.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="2.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="n">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="n">
         <v>115.6</v>
       </c>
-      <c r="C1" s="2" t="n">
+      <c r="C1" s="1" t="n">
         <v>114.4</v>
       </c>
       <c r="D1" s="3" t="n">
-        <f aca="false">ROUND(B1+C1,1)</f>
+        <f aca="false">B1+C1</f>
         <v>230</v>
       </c>
       <c r="E1" s="3" t="n">
         <v>110.8</v>
       </c>
       <c r="F1" s="3" t="n">
-        <f aca="false">ROUND(D1+E1,1)</f>
+        <f aca="false">D1+E1</f>
         <v>340.8</v>
       </c>
-      <c r="G1" s="0" t="n">
+      <c r="G1" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H1" s="0" t="n">
+      <c r="H1" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J1" s="4"/>
@@ -630,30 +637,30 @@
       <c r="L1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>112.1</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>112.8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <f aca="false">ROUND(B2+C2,1)</f>
+        <f aca="false">B2+C2</f>
         <v>224.9</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>114.5</v>
       </c>
       <c r="F2" s="3" t="n">
-        <f aca="false">ROUND(D2+E2,1)</f>
+        <f aca="false">D2+E2</f>
         <v>339.4</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J2" s="4"/>
@@ -661,30 +668,30 @@
       <c r="L2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>112.2</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>112.6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <f aca="false">ROUND(B3+C3,1)</f>
+        <f aca="false">B3+C3</f>
         <v>224.8</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>114.3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <f aca="false">ROUND(D3+E3,1)</f>
+        <f aca="false">D3+E3</f>
         <v>339.1</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="5"/>
@@ -692,30 +699,30 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>112.1</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>112.6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <f aca="false">ROUND(B4+C4,1)</f>
+        <f aca="false">B4+C4</f>
         <v>224.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>114.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <f aca="false">ROUND(D4+E4,1)</f>
+        <f aca="false">D4+E4</f>
         <v>339.5</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J4" s="4"/>
@@ -723,30 +730,30 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>112.1</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>112.4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <f aca="false">ROUND(B5+C5,1)</f>
+        <f aca="false">B5+C5</f>
         <v>224.5</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>111.7</v>
       </c>
       <c r="F5" s="3" t="n">
-        <f aca="false">ROUND(D5+E5,1)</f>
+        <f aca="false">D5+E5</f>
         <v>336.2</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="4"/>
@@ -754,30 +761,30 @@
       <c r="L5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>110.2</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>111.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <f aca="false">ROUND(B6+C6,1)</f>
+        <f aca="false">B6+C6</f>
         <v>221.5</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="F6" s="3" t="n">
-        <f aca="false">ROUND(D6+E6,1)</f>
+        <f aca="false">D6+E6</f>
         <v>332.1</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J6" s="4"/>
@@ -785,30 +792,30 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>-112.3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <f aca="false">ROUND(B7+C7,1)</f>
+        <f aca="false">B7+C7</f>
         <v>-112.3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>112</v>
       </c>
       <c r="F7" s="3" t="n">
-        <f aca="false">ROUND(D7+E7,1)</f>
-        <v>-0.3</v>
-      </c>
-      <c r="G7" s="0" t="n">
+        <f aca="false">D7+E7</f>
+        <v>-0.299999999999997</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="4"/>
@@ -822,185 +829,185 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>112.4</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="1" t="n">
         <v>112.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <f aca="false">ROUND(B9+C9,1)</f>
+        <f aca="false">B9+C9</f>
         <v>224.9</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>113.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <f aca="false">ROUND(D9+E9,1)</f>
+        <f aca="false">D9+E9</f>
         <v>338.3</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>112.4</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="1" t="n">
         <v>112.5</v>
       </c>
       <c r="D10" s="3" t="n">
-        <f aca="false">ROUND(B10+C10,1)</f>
+        <f aca="false">B10+C10</f>
         <v>224.9</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>113.2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <f aca="false">ROUND(D10+E10,1)</f>
+        <f aca="false">D10+E10</f>
         <v>338.1</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="8"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>112.4</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="1" t="n">
         <v>112.4</v>
       </c>
       <c r="D11" s="3" t="n">
-        <f aca="false">ROUND(B11+C11,1)</f>
+        <f aca="false">B11+C11</f>
         <v>224.8</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>113.6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <f aca="false">ROUND(D11+E11,1)</f>
+        <f aca="false">D11+E11</f>
         <v>338.4</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>110.7</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="1" t="n">
         <v>110.6</v>
       </c>
       <c r="D12" s="3" t="n">
-        <f aca="false">ROUND(B12+C12,1)</f>
+        <f aca="false">B12+C12</f>
         <v>221.3</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="F12" s="3" t="n">
-        <f aca="false">ROUND(D12+E12,1)</f>
+        <f aca="false">D12+E12</f>
         <v>333.4</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>110.8</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="1" t="n">
         <v>108.9</v>
       </c>
       <c r="D13" s="3" t="n">
-        <f aca="false">ROUND(B13+C13,1)</f>
+        <f aca="false">B13+C13</f>
         <v>219.7</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>110.7</v>
       </c>
       <c r="F13" s="3" t="n">
-        <f aca="false">ROUND(D13+E13,1)</f>
+        <f aca="false">D13+E13</f>
         <v>330.4</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J13" s="5"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>112.8</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <f aca="false">ROUND(B14+C14,1)</f>
+        <f aca="false">B14+C14</f>
         <v>112.8</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>110.3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <f aca="false">ROUND(D14+E14,1)</f>
+        <f aca="false">D14+E14</f>
         <v>223.1</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="4"/>
@@ -1008,61 +1015,61 @@
       <c r="L14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>112.5</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="1" t="n">
         <v>-110.9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <f aca="false">ROUND(B15+C15,1)</f>
-        <v>1.6</v>
+        <f aca="false">B15+C15</f>
+        <v>1.59999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>113.4</v>
       </c>
       <c r="F15" s="3" t="n">
-        <f aca="false">ROUND(D15+E15,1)</f>
+        <f aca="false">D15+E15</f>
         <v>115</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="n">
+      <c r="B16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <f aca="false">ROUND(B16+C16,1)</f>
+        <f aca="false">B16+C16</f>
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <f aca="false">ROUND(D16+E16,1)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="0" t="n">
+        <f aca="false">D16+E16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J16" s="4"/>
@@ -1070,33 +1077,33 @@
       <c r="L16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2" t="n">
+      <c r="B17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>-110.7</v>
       </c>
       <c r="D17" s="3" t="n">
-        <f aca="false">ROUND(B17+C17,1)</f>
+        <f aca="false">B17+C17</f>
         <v>-110.7</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>111.2</v>
       </c>
       <c r="F17" s="3" t="n">
-        <f aca="false">ROUND(D17+E17,1)</f>
+        <f aca="false">D17+E17</f>
         <v>0.5</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
@@ -1107,61 +1114,61 @@
       <c r="L18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="1" t="n">
         <v>112.2</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="1" t="n">
         <v>112.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <f aca="false">ROUND(B19+C19,1)</f>
+        <f aca="false">B19+C19</f>
         <v>224.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>111.3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <f aca="false">ROUND(D19+E19,1)</f>
+        <f aca="false">D19+E19</f>
         <v>335.7</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="K19" s="6"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="1" t="n">
         <v>111.1</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="1" t="n">
         <v>112.8</v>
       </c>
       <c r="D20" s="3" t="n">
-        <f aca="false">ROUND(B20+C20,1)</f>
+        <f aca="false">B20+C20</f>
         <v>223.9</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>108.5</v>
       </c>
       <c r="F20" s="3" t="n">
-        <f aca="false">ROUND(D20+E20,1)</f>
+        <f aca="false">D20+E20</f>
         <v>332.4</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J20" s="4"/>
@@ -1169,123 +1176,123 @@
       <c r="L20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="1" t="n">
         <v>110.9</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="1" t="n">
         <v>111.7</v>
       </c>
       <c r="D21" s="3" t="n">
-        <f aca="false">ROUND(B21+C21,1)</f>
+        <f aca="false">B21+C21</f>
         <v>222.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>115</v>
       </c>
       <c r="F21" s="3" t="n">
-        <f aca="false">ROUND(D21+E21,1)</f>
+        <f aca="false">D21+E21</f>
         <v>337.6</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="1" t="n">
         <v>110.8</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="1" t="n">
         <v>111.4</v>
       </c>
       <c r="D22" s="3" t="n">
-        <f aca="false">ROUND(B22+C22,1)</f>
+        <f aca="false">B22+C22</f>
         <v>222.2</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>112.5</v>
       </c>
       <c r="F22" s="3" t="n">
-        <f aca="false">ROUND(D22+E22,1)</f>
+        <f aca="false">D22+E22</f>
         <v>334.7</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J22" s="4"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="1" t="n">
         <v>110.7</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="1" t="n">
         <v>109.8</v>
       </c>
       <c r="D23" s="3" t="n">
-        <f aca="false">ROUND(B23+C23,1)</f>
+        <f aca="false">B23+C23</f>
         <v>220.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="F23" s="3" t="n">
-        <f aca="false">ROUND(D23+E23,1)</f>
+        <f aca="false">D23+E23</f>
         <v>331.1</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="G23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="L23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="1" t="n">
         <v>110.4</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="1" t="n">
         <v>109.9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <f aca="false">ROUND(B24+C24,1)</f>
+        <f aca="false">B24+C24</f>
         <v>220.3</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>112.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <f aca="false">ROUND(D24+E24,1)</f>
+        <f aca="false">D24+E24</f>
         <v>332.5</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="4"/>
@@ -1293,65 +1300,65 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="1" t="n">
         <v>112.1</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
-        <f aca="false">ROUND(B25+C25,1)</f>
+        <f aca="false">B25+C25</f>
         <v>112.1</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>110.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <f aca="false">ROUND(D25+E25,1)</f>
+        <f aca="false">D25+E25</f>
         <v>222.5</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="4"/>
-      <c r="K25" s="6"/>
+      <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="1" t="n">
         <v>112.9</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="1" t="n">
         <v>-112.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <f aca="false">ROUND(B26+C26,1)</f>
-        <v>0.1</v>
+        <f aca="false">B26+C26</f>
+        <v>0.100000000000009</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>112.5</v>
       </c>
       <c r="F26" s="3" t="n">
-        <f aca="false">ROUND(D26+E26,1)</f>
+        <f aca="false">D26+E26</f>
         <v>112.6</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="6"/>
       <c r="L26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1361,154 +1368,154 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="1" t="n">
         <v>113.8</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="1" t="n">
         <v>114.6</v>
       </c>
       <c r="D28" s="3" t="n">
-        <f aca="false">ROUND(B28+C28,1)</f>
+        <f aca="false">B28+C28</f>
         <v>228.4</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>116.3</v>
       </c>
       <c r="F28" s="3" t="n">
-        <f aca="false">ROUND(D28+E28,1)</f>
+        <f aca="false">D28+E28</f>
         <v>344.7</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
+      <c r="L28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="1" t="n">
         <v>113.8</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="1" t="n">
         <v>113.6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <f aca="false">ROUND(B29+C29,1)</f>
+        <f aca="false">B29+C29</f>
         <v>227.4</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>114.4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <f aca="false">ROUND(D29+E29,1)</f>
+        <f aca="false">D29+E29</f>
         <v>341.8</v>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="G29" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="0" t="n">
+      <c r="H29" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="5"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="1" t="n">
         <v>113.3</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="1" t="n">
         <v>113.4</v>
       </c>
       <c r="D30" s="3" t="n">
-        <f aca="false">ROUND(B30+C30,1)</f>
+        <f aca="false">B30+C30</f>
         <v>226.7</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>112.4</v>
       </c>
       <c r="F30" s="3" t="n">
-        <f aca="false">ROUND(D30+E30,1)</f>
+        <f aca="false">D30+E30</f>
         <v>339.1</v>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="0" t="n">
+      <c r="H30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="5"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="1" t="n">
         <v>113.6</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="1" t="n">
         <v>113</v>
       </c>
       <c r="D31" s="3" t="n">
-        <f aca="false">ROUND(B31+C31,1)</f>
+        <f aca="false">B31+C31</f>
         <v>226.6</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>113.7</v>
       </c>
       <c r="F31" s="3" t="n">
-        <f aca="false">ROUND(D31+E31,1)</f>
+        <f aca="false">D31+E31</f>
         <v>340.3</v>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="0" t="n">
+      <c r="H31" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="6"/>
+      <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="1" t="n">
         <v>113.1</v>
       </c>
       <c r="D32" s="3" t="n">
-        <f aca="false">ROUND(B32+C32,1)</f>
+        <f aca="false">B32+C32</f>
         <v>225.7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>114.4</v>
       </c>
       <c r="F32" s="3" t="n">
-        <f aca="false">ROUND(D32+E32,1)</f>
+        <f aca="false">D32+E32</f>
         <v>340.1</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J32" s="4"/>
@@ -1516,30 +1523,30 @@
       <c r="L32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="1" t="n">
         <v>108.8</v>
       </c>
       <c r="D33" s="3" t="n">
-        <f aca="false">ROUND(B33+C33,1)</f>
+        <f aca="false">B33+C33</f>
         <v>218.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <f aca="false">ROUND(D33+E33,1)</f>
+        <f aca="false">D33+E33</f>
         <v>218.8</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J33" s="4"/>
@@ -1547,65 +1554,65 @@
       <c r="L33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="1" t="n">
         <v>112.3</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="1" t="n">
         <v>-108.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <f aca="false">ROUND(B34+C34,1)</f>
+        <f aca="false">B34+C34</f>
         <v>3.7</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>110.7</v>
       </c>
       <c r="F34" s="3" t="n">
-        <f aca="false">ROUND(D34+E34,1)</f>
+        <f aca="false">D34+E34</f>
         <v>114.4</v>
       </c>
-      <c r="G34" s="0" t="n">
+      <c r="G34" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="0" t="n">
+      <c r="H34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="2" t="n">
+      <c r="B35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="n">
         <v>-112.5</v>
       </c>
       <c r="D35" s="3" t="n">
-        <f aca="false">ROUND(B35+C35,1)</f>
+        <f aca="false">B35+C35</f>
         <v>-112.5</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>111.2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <f aca="false">ROUND(D35+E35,1)</f>
+        <f aca="false">D35+E35</f>
         <v>-1.3</v>
       </c>
-      <c r="G35" s="0" t="n">
+      <c r="G35" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="0" t="n">
+      <c r="H35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="6"/>
       <c r="L35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1615,92 +1622,92 @@
       <c r="L36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="1" t="n">
         <v>111.8</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="1" t="n">
         <v>112.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <f aca="false">ROUND(B37+C37,1)</f>
+        <f aca="false">B37+C37</f>
         <v>224.5</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>115.6</v>
       </c>
       <c r="F37" s="3" t="n">
-        <f aca="false">ROUND(D37+E37,1)</f>
+        <f aca="false">D37+E37</f>
         <v>340.1</v>
       </c>
-      <c r="G37" s="0" t="n">
+      <c r="G37" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H37" s="0" t="n">
+      <c r="H37" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J37" s="5"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="1" t="n">
         <v>111.8</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
-        <f aca="false">ROUND(B38+C38,1)</f>
+        <f aca="false">B38+C38</f>
         <v>111.8</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>113.7</v>
       </c>
       <c r="F38" s="3" t="n">
-        <f aca="false">ROUND(D38+E38,1)</f>
+        <f aca="false">D38+E38</f>
         <v>225.5</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="4"/>
+      <c r="J38" s="5"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2" t="n">
+      <c r="B39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
-        <f aca="false">ROUND(B39+C39,1)</f>
+        <f aca="false">B39+C39</f>
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>115</v>
       </c>
       <c r="F39" s="3" t="n">
-        <f aca="false">ROUND(D39+E39,1)</f>
+        <f aca="false">D39+E39</f>
         <v>115</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="4"/>
@@ -1708,30 +1715,30 @@
       <c r="L39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="2" t="n">
+      <c r="B40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <f aca="false">ROUND(B40+C40,1)</f>
+        <f aca="false">B40+C40</f>
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>108.1</v>
       </c>
       <c r="F40" s="3" t="n">
-        <f aca="false">ROUND(D40+E40,1)</f>
+        <f aca="false">D40+E40</f>
         <v>108.1</v>
       </c>
-      <c r="G40" s="0" t="n">
+      <c r="G40" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H40" s="0" t="n">
+      <c r="H40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="4"/>
@@ -1739,30 +1746,30 @@
       <c r="L40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="2" t="n">
+      <c r="B41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <f aca="false">ROUND(B41+C41,1)</f>
+        <f aca="false">B41+C41</f>
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>116.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <f aca="false">ROUND(D41+E41,1)</f>
+        <f aca="false">D41+E41</f>
         <v>116.3</v>
       </c>
-      <c r="G41" s="0" t="n">
+      <c r="G41" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H41" s="0" t="n">
+      <c r="H41" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J41" s="4"/>
@@ -1770,61 +1777,61 @@
       <c r="L41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2" t="n">
+      <c r="B42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
-        <f aca="false">ROUND(B42+C42,1)</f>
+        <f aca="false">B42+C42</f>
         <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>110.5</v>
       </c>
       <c r="F42" s="3" t="n">
-        <f aca="false">ROUND(D42+E42,1)</f>
+        <f aca="false">D42+E42</f>
         <v>110.5</v>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H42" s="0" t="n">
+      <c r="H42" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="5"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2" t="n">
+      <c r="B43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
-        <f aca="false">ROUND(B43+C43,1)</f>
+        <f aca="false">B43+C43</f>
         <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>112.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <f aca="false">ROUND(D43+E43,1)</f>
+        <f aca="false">D43+E43</f>
         <v>112.3</v>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H43" s="0" t="n">
+      <c r="H43" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="5"/>
@@ -1832,61 +1839,61 @@
       <c r="L43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="2" t="n">
+      <c r="B44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1" t="n">
         <v>-113.3</v>
       </c>
       <c r="D44" s="3" t="n">
-        <f aca="false">ROUND(B44+C44,1)</f>
+        <f aca="false">B44+C44</f>
         <v>-113.3</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>114.9</v>
       </c>
       <c r="F44" s="3" t="n">
-        <f aca="false">ROUND(D44+E44,1)</f>
-        <v>1.6</v>
-      </c>
-      <c r="G44" s="0" t="n">
+        <f aca="false">D44+E44</f>
+        <v>1.60000000000001</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J44" s="4"/>
+      <c r="J44" s="5"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="2" t="n">
+      <c r="B45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="n">
         <v>-114.8</v>
       </c>
       <c r="D45" s="3" t="n">
-        <f aca="false">ROUND(B45+C45,1)</f>
+        <f aca="false">B45+C45</f>
         <v>-114.8</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>115.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <f aca="false">ROUND(D45+E45,1)</f>
-        <v>0.9</v>
-      </c>
-      <c r="G45" s="0" t="n">
+        <f aca="false">D45+E45</f>
+        <v>0.900000000000006</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H45" s="0" t="n">
+      <c r="H45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J45" s="4"/>
@@ -1900,92 +1907,92 @@
       <c r="L46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="1" t="n">
         <v>112.7</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="1" t="n">
         <v>112</v>
       </c>
       <c r="D47" s="3" t="n">
-        <f aca="false">ROUND(B47+C47,1)</f>
+        <f aca="false">B47+C47</f>
         <v>224.7</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>113.5</v>
       </c>
       <c r="F47" s="3" t="n">
-        <f aca="false">ROUND(D47+E47,1)</f>
+        <f aca="false">D47+E47</f>
         <v>338.2</v>
       </c>
-      <c r="G47" s="0" t="n">
+      <c r="G47" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H47" s="0" t="n">
+      <c r="H47" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="L47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="1" t="n">
         <v>110.8</v>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="1" t="n">
         <v>110.8</v>
       </c>
       <c r="D48" s="3" t="n">
-        <f aca="false">ROUND(B48+C48,1)</f>
+        <f aca="false">B48+C48</f>
         <v>221.6</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="F48" s="3" t="n">
-        <f aca="false">ROUND(D48+E48,1)</f>
+        <f aca="false">D48+E48</f>
         <v>333.4</v>
       </c>
-      <c r="G48" s="0" t="n">
+      <c r="G48" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H48" s="0" t="n">
+      <c r="H48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="1" t="n">
         <v>113.3</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="3" t="n">
-        <f aca="false">ROUND(B49+C49,1)</f>
+        <f aca="false">B49+C49</f>
         <v>113.3</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>112.6</v>
       </c>
       <c r="F49" s="3" t="n">
-        <f aca="false">ROUND(D49+E49,1)</f>
+        <f aca="false">D49+E49</f>
         <v>225.9</v>
       </c>
-      <c r="G49" s="0" t="n">
+      <c r="G49" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H49" s="0" t="n">
+      <c r="H49" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J49" s="4"/>
@@ -1993,30 +2000,30 @@
       <c r="L49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="1" t="n">
         <v>112.8</v>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
-        <f aca="false">ROUND(B50+C50,1)</f>
+        <f aca="false">B50+C50</f>
         <v>112.8</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>111.9</v>
       </c>
       <c r="F50" s="3" t="n">
-        <f aca="false">ROUND(D50+E50,1)</f>
+        <f aca="false">D50+E50</f>
         <v>224.7</v>
       </c>
-      <c r="G50" s="0" t="n">
+      <c r="G50" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H50" s="0" t="n">
+      <c r="H50" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J50" s="4"/>
@@ -2024,30 +2031,30 @@
       <c r="L50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="1" t="n">
         <v>112.3</v>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="1" t="n">
         <v>-109.5</v>
       </c>
       <c r="D51" s="3" t="n">
-        <f aca="false">ROUND(B51+C51,1)</f>
+        <f aca="false">B51+C51</f>
         <v>2.8</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>109.3</v>
       </c>
       <c r="F51" s="3" t="n">
-        <f aca="false">ROUND(D51+E51,1)</f>
+        <f aca="false">D51+E51</f>
         <v>112.1</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J51" s="4"/>
@@ -2055,30 +2062,30 @@
       <c r="L51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="1" t="n">
         <v>-112.2</v>
       </c>
       <c r="D52" s="3" t="n">
-        <f aca="false">ROUND(B52+C52,1)</f>
-        <v>0.4</v>
+        <f aca="false">B52+C52</f>
+        <v>0.399999999999992</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>112.4</v>
       </c>
       <c r="F52" s="3" t="n">
-        <f aca="false">ROUND(D52+E52,1)</f>
+        <f aca="false">D52+E52</f>
         <v>112.8</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H52" s="0" t="n">
+      <c r="H52" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J52" s="4"/>
@@ -2086,30 +2093,30 @@
       <c r="L52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="1" t="n">
         <v>-113.4</v>
       </c>
       <c r="D53" s="3" t="n">
-        <f aca="false">ROUND(B53+C53,1)</f>
-        <v>-0.4</v>
+        <f aca="false">B53+C53</f>
+        <v>-0.400000000000006</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>116</v>
       </c>
       <c r="F53" s="3" t="n">
-        <f aca="false">ROUND(D53+E53,1)</f>
+        <f aca="false">D53+E53</f>
         <v>115.6</v>
       </c>
-      <c r="G53" s="0" t="n">
+      <c r="G53" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H53" s="0" t="n">
+      <c r="H53" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J53" s="4"/>
@@ -2123,216 +2130,216 @@
       <c r="L54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="1" t="n">
         <v>111.9</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="1" t="n">
         <v>109.9</v>
       </c>
       <c r="D55" s="3" t="n">
-        <f aca="false">ROUND(B55+C55,1)</f>
+        <f aca="false">B55+C55</f>
         <v>221.8</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>107.5</v>
       </c>
       <c r="F55" s="3" t="n">
-        <f aca="false">ROUND(D55+E55,1)</f>
+        <f aca="false">D55+E55</f>
         <v>329.3</v>
       </c>
-      <c r="G55" s="0" t="n">
+      <c r="G55" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H55" s="0" t="n">
+      <c r="H55" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J55" s="4"/>
+      <c r="J55" s="5"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="8"/>
+      <c r="L55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="1" t="n">
         <v>111.3</v>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="1" t="n">
         <v>109.8</v>
       </c>
       <c r="D56" s="3" t="n">
-        <f aca="false">ROUND(B56+C56,1)</f>
+        <f aca="false">B56+C56</f>
         <v>221.1</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>115</v>
       </c>
       <c r="F56" s="3" t="n">
-        <f aca="false">ROUND(D56+E56,1)</f>
+        <f aca="false">D56+E56</f>
         <v>336.1</v>
       </c>
-      <c r="G56" s="0" t="n">
+      <c r="G56" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H56" s="0" t="n">
+      <c r="H56" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="6"/>
+      <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="1" t="n">
         <v>109.1</v>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="1" t="n">
         <v>110</v>
       </c>
       <c r="D57" s="3" t="n">
-        <f aca="false">ROUND(B57+C57,1)</f>
+        <f aca="false">B57+C57</f>
         <v>219.1</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>112</v>
       </c>
       <c r="F57" s="3" t="n">
-        <f aca="false">ROUND(D57+E57,1)</f>
+        <f aca="false">D57+E57</f>
         <v>331.1</v>
       </c>
-      <c r="G57" s="0" t="n">
+      <c r="G57" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H57" s="0" t="n">
+      <c r="H57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
+      <c r="L57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="1" t="n">
         <v>108.6</v>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="1" t="n">
         <v>109.5</v>
       </c>
       <c r="D58" s="3" t="n">
-        <f aca="false">ROUND(B58+C58,1)</f>
+        <f aca="false">B58+C58</f>
         <v>218.1</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>110.8</v>
       </c>
       <c r="F58" s="3" t="n">
-        <f aca="false">ROUND(D58+E58,1)</f>
+        <f aca="false">D58+E58</f>
         <v>328.9</v>
       </c>
-      <c r="G58" s="0" t="n">
+      <c r="G58" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H58" s="0" t="n">
+      <c r="H58" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+      <c r="K58" s="6"/>
       <c r="L58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="1" t="n">
         <v>109.1</v>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="1" t="n">
         <v>108.8</v>
       </c>
       <c r="D59" s="3" t="n">
-        <f aca="false">ROUND(B59+C59,1)</f>
+        <f aca="false">B59+C59</f>
         <v>217.9</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>108.7</v>
       </c>
       <c r="F59" s="3" t="n">
-        <f aca="false">ROUND(D59+E59,1)</f>
+        <f aca="false">D59+E59</f>
         <v>326.6</v>
       </c>
-      <c r="G59" s="0" t="n">
+      <c r="G59" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H59" s="0" t="n">
+      <c r="H59" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
-      <c r="L59" s="8"/>
+      <c r="L59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="1" t="n">
         <v>109.9</v>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="1" t="n">
         <v>107.7</v>
       </c>
       <c r="D60" s="3" t="n">
-        <f aca="false">ROUND(B60+C60,1)</f>
+        <f aca="false">B60+C60</f>
         <v>217.6</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="F60" s="3" t="n">
-        <f aca="false">ROUND(D60+E60,1)</f>
+        <f aca="false">D60+E60</f>
         <v>327.4</v>
       </c>
-      <c r="G60" s="0" t="n">
+      <c r="G60" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H60" s="0" t="n">
+      <c r="H60" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="5"/>
+      <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="1" t="n">
         <v>108.8</v>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="1" t="n">
         <v>108.4</v>
       </c>
       <c r="D61" s="3" t="n">
-        <f aca="false">ROUND(B61+C61,1)</f>
+        <f aca="false">B61+C61</f>
         <v>217.2</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>109.6</v>
       </c>
       <c r="F61" s="3" t="n">
-        <f aca="false">ROUND(D61+E61,1)</f>
+        <f aca="false">D61+E61</f>
         <v>326.8</v>
       </c>
-      <c r="G61" s="0" t="n">
+      <c r="G61" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H61" s="0" t="n">
+      <c r="H61" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J61" s="4"/>
@@ -2340,30 +2347,30 @@
       <c r="L61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="1" t="n">
         <v>107.2</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="1" t="n">
         <v>108.2</v>
       </c>
       <c r="D62" s="3" t="n">
-        <f aca="false">ROUND(B62+C62,1)</f>
+        <f aca="false">B62+C62</f>
         <v>215.4</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="F62" s="3" t="n">
-        <f aca="false">ROUND(D62+E62,1)</f>
+        <f aca="false">D62+E62</f>
         <v>327.2</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H62" s="0" t="n">
+      <c r="H62" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J62" s="4"/>
@@ -2371,30 +2378,30 @@
       <c r="L62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="1" t="n">
         <v>109.9</v>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="3" t="n">
-        <f aca="false">ROUND(B63+C63,1)</f>
+        <f aca="false">B63+C63</f>
         <v>109.9</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <f aca="false">ROUND(D63+E63,1)</f>
+        <f aca="false">D63+E63</f>
         <v>109.9</v>
       </c>
-      <c r="G63" s="0" t="n">
+      <c r="G63" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H63" s="0" t="n">
+      <c r="H63" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J63" s="4"/>
@@ -2402,30 +2409,30 @@
       <c r="L63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="1" t="n">
         <v>109.7</v>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <f aca="false">ROUND(B64+C64,1)</f>
+        <f aca="false">B64+C64</f>
         <v>109.7</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>108.6</v>
       </c>
       <c r="F64" s="3" t="n">
-        <f aca="false">ROUND(D64+E64,1)</f>
+        <f aca="false">D64+E64</f>
         <v>218.3</v>
       </c>
-      <c r="G64" s="0" t="n">
+      <c r="G64" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H64" s="0" t="n">
+      <c r="H64" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J64" s="4"/>
@@ -2433,35 +2440,35 @@
       <c r="L64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="1" t="n">
         <v>109.9</v>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="1" t="n">
         <v>-112.1</v>
       </c>
       <c r="D65" s="3" t="n">
-        <f aca="false">ROUND(B65+C65,1)</f>
-        <v>-2.2</v>
+        <f aca="false">B65+C65</f>
+        <v>-2.19999999999999</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>107.8</v>
       </c>
       <c r="F65" s="3" t="n">
-        <f aca="false">ROUND(D65+E65,1)</f>
+        <f aca="false">D65+E65</f>
         <v>105.6</v>
       </c>
-      <c r="G65" s="0" t="n">
+      <c r="G65" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H65" s="0" t="n">
+      <c r="H65" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
+      <c r="L65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D66" s="7"/>
@@ -2470,30 +2477,30 @@
       <c r="L66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="1" t="n">
         <v>113.3</v>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="1" t="n">
         <v>112.7</v>
       </c>
       <c r="D67" s="3" t="n">
-        <f aca="false">ROUND(B67+C67,1)</f>
+        <f aca="false">B67+C67</f>
         <v>226</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>111.6</v>
       </c>
       <c r="F67" s="3" t="n">
-        <f aca="false">ROUND(D67+E67,1)</f>
+        <f aca="false">D67+E67</f>
         <v>337.6</v>
       </c>
-      <c r="G67" s="0" t="n">
+      <c r="G67" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H67" s="0" t="n">
+      <c r="H67" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J67" s="4"/>
@@ -2501,92 +2508,92 @@
       <c r="L67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="1" t="n">
         <v>113.2</v>
       </c>
       <c r="D68" s="3" t="n">
-        <f aca="false">ROUND(B68+C68,1)</f>
+        <f aca="false">B68+C68</f>
         <v>225.8</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>115.7</v>
       </c>
       <c r="F68" s="3" t="n">
-        <f aca="false">ROUND(D68+E68,1)</f>
+        <f aca="false">D68+E68</f>
         <v>341.5</v>
       </c>
-      <c r="G68" s="0" t="n">
+      <c r="G68" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H68" s="0" t="n">
+      <c r="H68" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
+      <c r="K68" s="6"/>
       <c r="L68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="1" t="n">
         <v>112.7</v>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="1" t="n">
         <v>112.2</v>
       </c>
       <c r="D69" s="3" t="n">
-        <f aca="false">ROUND(B69+C69,1)</f>
+        <f aca="false">B69+C69</f>
         <v>224.9</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>112.7</v>
       </c>
       <c r="F69" s="3" t="n">
-        <f aca="false">ROUND(D69+E69,1)</f>
+        <f aca="false">D69+E69</f>
         <v>337.6</v>
       </c>
-      <c r="G69" s="0" t="n">
+      <c r="G69" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H69" s="0" t="n">
+      <c r="H69" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="6"/>
+      <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="1" t="n">
         <v>112.3</v>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="1" t="n">
         <v>112.4</v>
       </c>
       <c r="D70" s="3" t="n">
-        <f aca="false">ROUND(B70+C70,1)</f>
+        <f aca="false">B70+C70</f>
         <v>224.7</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="F70" s="3" t="n">
-        <f aca="false">ROUND(D70+E70,1)</f>
+        <f aca="false">D70+E70</f>
         <v>336.5</v>
       </c>
-      <c r="G70" s="0" t="n">
+      <c r="G70" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H70" s="0" t="n">
+      <c r="H70" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="4"/>
@@ -2594,30 +2601,30 @@
       <c r="L70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="1" t="n">
         <v>112.9</v>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="1" t="n">
         <v>-111.1</v>
       </c>
       <c r="D71" s="3" t="n">
-        <f aca="false">ROUND(B71+C71,1)</f>
-        <v>1.8</v>
+        <f aca="false">B71+C71</f>
+        <v>1.80000000000001</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="F71" s="3" t="n">
-        <f aca="false">ROUND(D71+E71,1)</f>
+        <f aca="false">D71+E71</f>
         <v>112.4</v>
       </c>
-      <c r="G71" s="0" t="n">
+      <c r="G71" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H71" s="0" t="n">
+      <c r="H71" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J71" s="4"/>
@@ -2625,61 +2632,61 @@
       <c r="L71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="1" t="n">
         <v>-112</v>
       </c>
       <c r="D72" s="3" t="n">
-        <f aca="false">ROUND(B72+C72,1)</f>
-        <v>0.6</v>
+        <f aca="false">B72+C72</f>
+        <v>0.599999999999994</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>112.7</v>
       </c>
       <c r="F72" s="3" t="n">
-        <f aca="false">ROUND(D72+E72,1)</f>
+        <f aca="false">D72+E72</f>
         <v>113.3</v>
       </c>
-      <c r="G72" s="0" t="n">
+      <c r="G72" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H72" s="0" t="n">
+      <c r="H72" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J72" s="4"/>
+      <c r="J72" s="5"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="1" t="n">
         <v>110.2</v>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="1" t="n">
         <v>-111.2</v>
       </c>
       <c r="D73" s="3" t="n">
-        <f aca="false">ROUND(B73+C73,1)</f>
+        <f aca="false">B73+C73</f>
         <v>-1</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>114.9</v>
       </c>
       <c r="F73" s="3" t="n">
-        <f aca="false">ROUND(D73+E73,1)</f>
+        <f aca="false">D73+E73</f>
         <v>113.9</v>
       </c>
-      <c r="G73" s="0" t="n">
+      <c r="G73" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H73" s="0" t="n">
+      <c r="H73" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J73" s="4"/>
@@ -2687,33 +2694,33 @@
       <c r="L73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="2" t="n">
+      <c r="B74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1" t="n">
         <v>-113.8</v>
       </c>
       <c r="D74" s="3" t="n">
-        <f aca="false">ROUND(B74+C74,1)</f>
+        <f aca="false">B74+C74</f>
         <v>-113.8</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>119.4</v>
       </c>
       <c r="F74" s="3" t="n">
-        <f aca="false">ROUND(D74+E74,1)</f>
-        <v>5.6</v>
-      </c>
-      <c r="G74" s="0" t="n">
+        <f aca="false">D74+E74</f>
+        <v>5.60000000000001</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H74" s="0" t="n">
+      <c r="H74" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J74" s="5"/>
+      <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
     </row>
@@ -2724,30 +2731,30 @@
       <c r="L75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="1" t="n">
         <v>113.7</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="1" t="n">
         <v>114.4</v>
       </c>
       <c r="D76" s="3" t="n">
-        <f aca="false">ROUND(B76+C76,1)</f>
+        <f aca="false">B76+C76</f>
         <v>228.1</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="F76" s="3" t="n">
-        <f aca="false">ROUND(D76+E76,1)</f>
+        <f aca="false">D76+E76</f>
         <v>343.5</v>
       </c>
-      <c r="G76" s="0" t="n">
+      <c r="G76" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H76" s="0" t="n">
+      <c r="H76" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J76" s="4"/>
@@ -2755,30 +2762,30 @@
       <c r="L76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="1" t="n">
         <v>111.9</v>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="1" t="n">
         <v>112.5</v>
       </c>
       <c r="D77" s="3" t="n">
-        <f aca="false">ROUND(B77+C77,1)</f>
+        <f aca="false">B77+C77</f>
         <v>224.4</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>114.7</v>
       </c>
       <c r="F77" s="3" t="n">
-        <f aca="false">ROUND(D77+E77,1)</f>
+        <f aca="false">D77+E77</f>
         <v>339.1</v>
       </c>
-      <c r="G77" s="0" t="n">
+      <c r="G77" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H77" s="0" t="n">
+      <c r="H77" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J77" s="4"/>
@@ -2786,30 +2793,30 @@
       <c r="L77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="1" t="n">
         <v>111.9</v>
       </c>
       <c r="D78" s="3" t="n">
-        <f aca="false">ROUND(B78+C78,1)</f>
+        <f aca="false">B78+C78</f>
         <v>223.9</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>113.5</v>
       </c>
       <c r="F78" s="3" t="n">
-        <f aca="false">ROUND(D78+E78,1)</f>
+        <f aca="false">D78+E78</f>
         <v>337.4</v>
       </c>
-      <c r="G78" s="0" t="n">
+      <c r="G78" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H78" s="0" t="n">
+      <c r="H78" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J78" s="4"/>
@@ -2817,30 +2824,30 @@
       <c r="L78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <f aca="false">ROUND(B79+C79,1)</f>
+        <f aca="false">B79+C79</f>
         <v>112.6</v>
       </c>
       <c r="E79" s="3" t="n">
         <v>110.9</v>
       </c>
       <c r="F79" s="3" t="n">
-        <f aca="false">ROUND(D79+E79,1)</f>
+        <f aca="false">D79+E79</f>
         <v>223.5</v>
       </c>
-      <c r="G79" s="0" t="n">
+      <c r="G79" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H79" s="0" t="n">
+      <c r="H79" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J79" s="4"/>
@@ -2848,30 +2855,30 @@
       <c r="L79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="1" t="n">
         <v>112.6</v>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <f aca="false">ROUND(B80+C80,1)</f>
+        <f aca="false">B80+C80</f>
         <v>112.6</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>110.8</v>
       </c>
       <c r="F80" s="3" t="n">
-        <f aca="false">ROUND(D80+E80,1)</f>
+        <f aca="false">D80+E80</f>
         <v>223.4</v>
       </c>
-      <c r="G80" s="0" t="n">
+      <c r="G80" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H80" s="0" t="n">
+      <c r="H80" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J80" s="4"/>
@@ -2879,30 +2886,30 @@
       <c r="L80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="1" t="n">
         <v>112.4</v>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <f aca="false">ROUND(B81+C81,1)</f>
+        <f aca="false">B81+C81</f>
         <v>112.4</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>112.6</v>
       </c>
       <c r="F81" s="3" t="n">
-        <f aca="false">ROUND(D81+E81,1)</f>
+        <f aca="false">D81+E81</f>
         <v>225</v>
       </c>
-      <c r="G81" s="0" t="n">
+      <c r="G81" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H81" s="0" t="n">
+      <c r="H81" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J81" s="4"/>
@@ -2910,30 +2917,30 @@
       <c r="L81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="1" t="n">
         <v>112.3</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <f aca="false">ROUND(B82+C82,1)</f>
+        <f aca="false">B82+C82</f>
         <v>112.3</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>110.4</v>
       </c>
       <c r="F82" s="3" t="n">
-        <f aca="false">ROUND(D82+E82,1)</f>
+        <f aca="false">D82+E82</f>
         <v>222.7</v>
       </c>
-      <c r="G82" s="0" t="n">
+      <c r="G82" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H82" s="0" t="n">
+      <c r="H82" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J82" s="4"/>
@@ -2941,30 +2948,30 @@
       <c r="L82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="1" t="n">
         <v>111.9</v>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <f aca="false">ROUND(B83+C83,1)</f>
+        <f aca="false">B83+C83</f>
         <v>111.9</v>
       </c>
       <c r="E83" s="3" t="n">
         <v>108.4</v>
       </c>
       <c r="F83" s="3" t="n">
-        <f aca="false">ROUND(D83+E83,1)</f>
+        <f aca="false">D83+E83</f>
         <v>220.3</v>
       </c>
-      <c r="G83" s="0" t="n">
+      <c r="G83" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H83" s="0" t="n">
+      <c r="H83" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="4"/>
@@ -2972,30 +2979,30 @@
       <c r="L83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="1" t="n">
         <v>111.9</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <f aca="false">ROUND(B84+C84,1)</f>
+        <f aca="false">B84+C84</f>
         <v>111.9</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="F84" s="3" t="n">
-        <f aca="false">ROUND(D84+E84,1)</f>
+        <f aca="false">D84+E84</f>
         <v>223.7</v>
       </c>
-      <c r="G84" s="0" t="n">
+      <c r="G84" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H84" s="0" t="n">
+      <c r="H84" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J84" s="4"/>
@@ -3003,30 +3010,30 @@
       <c r="L84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="2" t="n">
+      <c r="B85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <f aca="false">ROUND(B85+C85,1)</f>
+        <f aca="false">B85+C85</f>
         <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <f aca="false">ROUND(D85+E85,1)</f>
-        <v>0</v>
-      </c>
-      <c r="G85" s="0" t="n">
+        <f aca="false">D85+E85</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H85" s="0" t="n">
+      <c r="H85" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J85" s="4"/>
